--- a/ZonasEscolares/excels/LIMA-CAÑETE-SAN_VICENTE_DE_CAÑETE.xlsx
+++ b/ZonasEscolares/excels/LIMA-CAÑETE-SAN_VICENTE_DE_CAÑETE.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAN_VICENTE_DE_CAÑETE</t>
+          <t>SAN VICENTE DE CAÑETE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-CAÑETE-SAN_VICENTE_DE_CAÑETE.xlsx
+++ b/ZonasEscolares/excels/LIMA-CAÑETE-SAN_VICENTE_DE_CAÑETE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>023</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-13.08492</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.38731</v>
-      </c>
-      <c r="I2" t="n">
-        <v>270</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-13.08492</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.38731</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>481</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-13.07862</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.38379999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>235</v>
-      </c>
-      <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-13.07862</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.3838</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>501 MEDALLA MILAGROSA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-13.07556</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.38423</v>
-      </c>
-      <c r="I4" t="n">
-        <v>268</v>
-      </c>
-      <c r="J4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-13.07556</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.38423</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>20874</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-13.07634</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.38625999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1350</v>
-      </c>
-      <c r="J5" t="n">
-        <v>55</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-13.07634</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.38626</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>20188</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-13.0791</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.3841</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1592</v>
-      </c>
-      <c r="J6" t="n">
-        <v>73</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-13.0791</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.3841</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1592</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>20189 NUESTRA SEÑORA DE LA CONCEPCION / 617</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-13.07468</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.38602</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1394</v>
-      </c>
-      <c r="J7" t="n">
-        <v>60</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-13.07468</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.38602</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1394</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>20190 REPUBLICA DE CHILE</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-13.08214</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.38711000000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>617</v>
-      </c>
-      <c r="J8" t="n">
-        <v>28</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-13.08214</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.38711</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>20191 ALFONSO UGARTE</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-13.0772</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.38144</v>
-      </c>
-      <c r="I9" t="n">
-        <v>509</v>
-      </c>
-      <c r="J9" t="n">
-        <v>26</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-13.0772</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.38144</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>20193</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-13.07349</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.38082</v>
-      </c>
-      <c r="I10" t="n">
-        <v>345</v>
-      </c>
-      <c r="J10" t="n">
-        <v>16</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-13.07349</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.38082</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>20957</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-13.07507</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.38720000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>604</v>
-      </c>
-      <c r="J11" t="n">
-        <v>26</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-13.07507</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.3872</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>JOSE BUENAVENTURA SEPULVEDA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-13.07666</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.38925</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1451</v>
-      </c>
-      <c r="J12" t="n">
-        <v>91</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-13.07666</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.38925</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1451</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>SANTA RITA DE CASSIA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-13.08496</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.38696</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1041</v>
-      </c>
-      <c r="J13" t="n">
-        <v>64</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-13.08496</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.38696</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>VICTORIA BARCIA BONIFFATTI</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-13.07398</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.37555999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>772</v>
-      </c>
-      <c r="J14" t="n">
-        <v>47</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-13.07398</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.37556</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>ROSA DE SANTA MARIA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-13.07596</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.37905000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>322</v>
-      </c>
-      <c r="J15" t="n">
-        <v>38</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-13.07596</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.37905</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>MATER CHRISTI</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-13.07555</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.38844</v>
-      </c>
-      <c r="I16" t="n">
-        <v>647</v>
-      </c>
-      <c r="J16" t="n">
-        <v>38</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-13.07555</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.38844</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>JOSE MARIA EGUREN</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-13.0724</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.38648999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>316</v>
-      </c>
-      <c r="J17" t="n">
-        <v>24</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-13.0724</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.38649</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>MARIA ENRIQUETA DOMINICI</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-13.07249</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.38225</v>
-      </c>
-      <c r="I18" t="n">
-        <v>263</v>
-      </c>
-      <c r="J18" t="n">
-        <v>19</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-13.07249</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.38225</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>REYNA DE LOS ANGELES</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-13.02597</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.47944</v>
-      </c>
-      <c r="I19" t="n">
-        <v>235</v>
-      </c>
-      <c r="J19" t="n">
-        <v>12</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-13.02597</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.47944</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>20960</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.542136</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.721557</v>
-      </c>
-      <c r="I20" t="n">
-        <v>208</v>
-      </c>
-      <c r="J20" t="n">
-        <v>8</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.542136</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.721557</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>VIRGEN DE LA CANDELARIA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.51761</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.73491</v>
-      </c>
-      <c r="I21" t="n">
-        <v>204</v>
-      </c>
-      <c r="J21" t="n">
-        <v>9</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.51761</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.73491</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>20147 ELADIO HURTADO VICENTE</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-13.061447</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.34666799999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1156</v>
-      </c>
-      <c r="J22" t="n">
-        <v>62</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-13.061447</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.346668</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1156</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>IMPERIAL C.N.I.</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-13.064703</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.352767</v>
-      </c>
-      <c r="I23" t="n">
-        <v>542</v>
-      </c>
-      <c r="J23" t="n">
-        <v>38</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-13.064703</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.352767</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>CORONEL FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-13.06428</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-76.35575</v>
-      </c>
-      <c r="I24" t="n">
-        <v>224</v>
-      </c>
-      <c r="J24" t="n">
-        <v>18</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-13.06428</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-76.35575</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>21505 NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-13.03945</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.35089000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>354</v>
-      </c>
-      <c r="J25" t="n">
-        <v>16</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-13.03945</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.35089</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>21504 SAN JOSE / SAN JOSE</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-13.039766</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.351249</v>
-      </c>
-      <c r="I26" t="n">
-        <v>963</v>
-      </c>
-      <c r="J26" t="n">
-        <v>51</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-13.039766</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.351249</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>20167 MANUEL GONZALES PRADA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-13.017297</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.33846</v>
-      </c>
-      <c r="I27" t="n">
-        <v>854</v>
-      </c>
-      <c r="J27" t="n">
-        <v>39</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-13.017297</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.33846</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>20176</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.975075</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.404409</v>
-      </c>
-      <c r="I28" t="n">
-        <v>518</v>
-      </c>
-      <c r="J28" t="n">
-        <v>26</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.975075</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.404409</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.9432</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.384</v>
-      </c>
-      <c r="I29" t="n">
-        <v>700</v>
-      </c>
-      <c r="J29" t="n">
-        <v>35</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.9432</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.384</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>20194 JESUS DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.614426</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-76.645582</v>
-      </c>
-      <c r="I30" t="n">
-        <v>287</v>
-      </c>
-      <c r="J30" t="n">
-        <v>22</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.614426</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-76.645582</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>VILLA MARIA</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-13.065854</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-76.354992</v>
-      </c>
-      <c r="I31" t="n">
-        <v>616</v>
-      </c>
-      <c r="J31" t="n">
-        <v>24</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-13.065854</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-76.354992</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>GEUNI</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-13.07559</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-76.37633</v>
-      </c>
-      <c r="I32" t="n">
-        <v>895</v>
-      </c>
-      <c r="J32" t="n">
-        <v>38</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-13.07559</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-76.37633</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>MAZUBA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-13.07775</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.387429</v>
-      </c>
-      <c r="I33" t="n">
-        <v>418</v>
-      </c>
-      <c r="J33" t="n">
-        <v>30</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-13.07775</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.387429</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>EVARISTE GALOIS</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-13.07686</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.389529</v>
-      </c>
-      <c r="I34" t="n">
-        <v>701</v>
-      </c>
-      <c r="J34" t="n">
-        <v>48</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-13.07686</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.389529</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>21531 MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-13.1357</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-76.3455</v>
-      </c>
-      <c r="I35" t="n">
-        <v>590</v>
-      </c>
-      <c r="J35" t="n">
-        <v>31</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-13.1357</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-76.3455</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>20975 ANDRES AVELINO CACERES DORREGARAY / 637</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-13.291588</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-76.24701399999999</v>
-      </c>
-      <c r="I36" t="n">
-        <v>329</v>
-      </c>
-      <c r="J36" t="n">
-        <v>19</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-13.291588</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-76.247014</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>MARYLAND BILINGUAL HIGH SCHOOL</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-13.0837</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-76.38883300000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>645</v>
-      </c>
-      <c r="J37" t="n">
-        <v>32</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-13.0837</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-76.388833</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>PROLOG DE CAÑETE</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-13.06591</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.35438000000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>406</v>
-      </c>
-      <c r="J38" t="n">
-        <v>42</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-13.06591</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.35438</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>ISAAC NEWTON SCHOOL CHILCA</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.518595</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-76.73821100000001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>325</v>
-      </c>
-      <c r="J39" t="n">
-        <v>14</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.518595</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-76.738211</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>MI NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-13.078387</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-76.38684499999999</v>
-      </c>
-      <c r="I40" t="n">
-        <v>212</v>
-      </c>
-      <c r="J40" t="n">
-        <v>13</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-13.078387</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-76.386845</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-CAÑETE-SAN_VICENTE_DE_CAÑETE.xlsx
+++ b/ZonasEscolares/excels/LIMA-CAÑETE-SAN_VICENTE_DE_CAÑETE.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>351682</t>
+          <t>351795</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>023</t>
+          <t>501 MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.08492</t>
+          <t>-13.07556</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.38731</t>
+          <t>-76.38423</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>268</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,22 +563,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>351757</t>
+          <t>352653</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>REYNA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.07862</t>
+          <t>-13.02597</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.3838</t>
+          <t>-76.47944</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>351795</t>
+          <t>351682</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>501 MEDALLA MILAGROSA</t>
+          <t>023</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.07556</t>
+          <t>-13.08492</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.38423</t>
+          <t>-76.38731</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>351804</t>
+          <t>907889</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>MI NIÑO JESUS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-13.07634</t>
+          <t>-13.078387</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.38626</t>
+          <t>-76.386845</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>351861</t>
+          <t>858704</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>ISAAC NEWTON SCHOOL CHILCA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-13.0791</t>
+          <t>-12.518595</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.3841</t>
+          <t>-76.738211</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>351875</t>
+          <t>351903</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20189 NUESTRA SEÑORA DE LA CONCEPCION / 617</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.07468</t>
+          <t>-13.07349</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.38602</t>
+          <t>-76.38082</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>345</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>351880</t>
+          <t>353252</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20190 REPUBLICA DE CHILE</t>
+          <t>21505 NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.08214</t>
+          <t>-13.03945</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.38711</t>
+          <t>-76.35089</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>354</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>351899</t>
+          <t>353214</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20191 ALFONSO UGARTE</t>
+          <t>CORONEL FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.0772</t>
+          <t>-13.06428</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.38144</t>
+          <t>-76.35575</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>351903</t>
+          <t>352243</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>MARIA ENRIQUETA DOMINICI</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.07349</t>
+          <t>-13.07249</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.38082</t>
+          <t>-76.38225</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>263</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>351960</t>
+          <t>730697</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>20975 ANDRES AVELINO CACERES DORREGARAY / 637</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.07507</t>
+          <t>-13.291588</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.3872</t>
+          <t>-76.247014</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>352002</t>
+          <t>354464</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JOSE BUENAVENTURA SEPULVEDA</t>
+          <t>20194 JESUS DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.07666</t>
+          <t>-12.614426</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.38925</t>
+          <t>-76.645582</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>287</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>352021</t>
+          <t>352177</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SANTA RITA DE CASSIA</t>
+          <t>JOSE MARIA EGUREN</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.08496</t>
+          <t>-13.0724</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.38696</t>
+          <t>-76.38649</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>316</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>352097</t>
+          <t>540174</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VICTORIA BARCIA BONIFFATTI</t>
+          <t>VILLA MARIA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.07398</t>
+          <t>-13.065854</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.37556</t>
+          <t>-76.354992</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>616</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>352144</t>
+          <t>351899</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ROSA DE SANTA MARIA</t>
+          <t>20191 ALFONSO UGARTE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.07596</t>
+          <t>-13.0772</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.37905</t>
+          <t>-76.38144</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>509</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>352163</t>
+          <t>351960</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MATER CHRISTI</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.07555</t>
+          <t>-13.07507</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.38844</t>
+          <t>-76.3872</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>604</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>352177</t>
+          <t>354138</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JOSE MARIA EGUREN</t>
+          <t>20176</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.0724</t>
+          <t>-12.975075</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.38649</t>
+          <t>-76.404409</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>518</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>352243</t>
+          <t>351880</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MARIA ENRIQUETA DOMINICI</t>
+          <t>20190 REPUBLICA DE CHILE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.07249</t>
+          <t>-13.08214</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.38225</t>
+          <t>-76.38711</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>617</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>352653</t>
+          <t>644671</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>REYNA DE LOS ANGELES</t>
+          <t>MAZUBA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.02597</t>
+          <t>-13.07775</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.47944</t>
+          <t>-76.387429</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>418</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>352728</t>
+          <t>730230</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>21531 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.542136</t>
+          <t>-13.1357</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.721557</t>
+          <t>-76.3455</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>590</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>352813</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA CANDELARIA</t>
+          <t>MARYLAND BILINGUAL HIGH SCHOOL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.51761</t>
+          <t>-13.0837</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.73491</t>
+          <t>-76.388833</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>645</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>353030</t>
+          <t>354204</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20147 ELADIO HURTADO VICENTE</t>
+          <t>MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.061447</t>
+          <t>-12.9432</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.346668</t>
+          <t>-76.384</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>700</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,27 +1803,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>353068</t>
+          <t>352144</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IMPERIAL C.N.I.</t>
+          <t>ROSA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.064703</t>
+          <t>-13.07596</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.352767</t>
+          <t>-76.37905</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>322</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>353214</t>
+          <t>352163</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CORONEL FRANCISCO BOLOGNESI</t>
+          <t>MATER CHRISTI</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-13.06428</t>
+          <t>-13.07555</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.35575</t>
+          <t>-76.38844</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>647</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>353252</t>
+          <t>353068</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>21505 NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>IMPERIAL C.N.I.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-13.03945</t>
+          <t>-13.064703</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.35089</t>
+          <t>-76.352767</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>542</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>353266</t>
+          <t>621561</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>21504 SAN JOSE / SAN JOSE</t>
+          <t>GEUNI</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-13.039766</t>
+          <t>-13.07559</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.351249</t>
+          <t>-76.37633</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>895</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>354138</t>
+          <t>830932</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20176</t>
+          <t>PROLOG DE CAÑETE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.975075</t>
+          <t>-13.06591</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.404409</t>
+          <t>-76.35438</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>406</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>354204</t>
+          <t>352097</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU</t>
+          <t>VICTORIA BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.9432</t>
+          <t>-13.07398</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.384</t>
+          <t>-76.37556</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>772</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>354464</t>
+          <t>730193</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20194 JESUS DIVINO MAESTRO</t>
+          <t>EVARISTE GALOIS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.614426</t>
+          <t>-13.07686</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.645582</t>
+          <t>-76.389529</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>701</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>540174</t>
+          <t>353266</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>VILLA MARIA</t>
+          <t>21504 SAN JOSE / SAN JOSE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-13.065854</t>
+          <t>-13.039766</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.354992</t>
+          <t>-76.351249</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>963</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>621561</t>
+          <t>351804</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GEUNI</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-13.07559</t>
+          <t>-13.07634</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.37633</t>
+          <t>-76.38626</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>644671</t>
+          <t>351875</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MAZUBA</t>
+          <t>20189 NUESTRA SEÑORA DE LA CONCEPCION / 617</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-13.07775</t>
+          <t>-13.07468</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.387429</t>
+          <t>-76.38602</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>730193</t>
+          <t>353030</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EVARISTE GALOIS</t>
+          <t>20147 ELADIO HURTADO VICENTE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-13.07686</t>
+          <t>-13.061447</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.389529</t>
+          <t>-76.346668</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>730230</t>
+          <t>352021</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>21531 MARIA AUXILIADORA</t>
+          <t>SANTA RITA DE CASSIA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-13.1357</t>
+          <t>-13.08496</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.3455</t>
+          <t>-76.38696</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>730697</t>
+          <t>351861</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20975 ANDRES AVELINO CACERES DORREGARAY / 637</t>
+          <t>20188</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-13.291588</t>
+          <t>-13.0791</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.247014</t>
+          <t>-76.3841</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>352728</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MARYLAND BILINGUAL HIGH SCHOOL</t>
+          <t>20960</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-13.0837</t>
+          <t>-12.542136</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.388833</t>
+          <t>-76.721557</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>830932</t>
+          <t>351757</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PROLOG DE CAÑETE</t>
+          <t>481</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-13.06591</t>
+          <t>-13.07862</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.35438</t>
+          <t>-76.3838</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>858704</t>
+          <t>352813</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON SCHOOL CHILCA</t>
+          <t>VIRGEN DE LA CANDELARIA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.518595</t>
+          <t>-12.51761</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.738211</t>
+          <t>-76.73491</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>907889</t>
+          <t>352002</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MI NIÑO JESUS</t>
+          <t>JOSE BUENAVENTURA SEPULVEDA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-13.078387</t>
+          <t>-13.07666</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.386845</t>
+          <t>-76.38925</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-CAÑETE-SAN_VICENTE_DE_CAÑETE.xlsx
+++ b/ZonasEscolares/excels/LIMA-CAÑETE-SAN_VICENTE_DE_CAÑETE.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>351795</t>
+          <t>907889</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>501 MEDALLA MILAGROSA</t>
+          <t>MI NIÑO JESUS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.07556</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.38423</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>-13.078387</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.386845</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>352653</t>
+          <t>858704</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>REYNA DE LOS ANGELES</t>
+          <t>ISAAC NEWTON SCHOOL CHILCA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.02597</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.47944</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-12.518595</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.738211</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>351682</t>
+          <t>830932</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>023</t>
+          <t>PROLOG DE CAÑETE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.08492</t>
+          <t>406</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.38731</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>-13.06591</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.35438</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>907889</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MI NIÑO JESUS</t>
+          <t>MARYLAND BILINGUAL HIGH SCHOOL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-13.078387</t>
+          <t>645</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.386845</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-13.0837</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.388833</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>858704</t>
+          <t>730697</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON SCHOOL CHILCA</t>
+          <t>20975 ANDRES AVELINO CACERES DORREGARAY / 637</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.518595</t>
+          <t>329</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.738211</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>-13.291588</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.247014</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>351903</t>
+          <t>730230</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>21531 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.07349</t>
+          <t>590</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.38082</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>-13.1357</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.3455</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>353252</t>
+          <t>730193</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21505 NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>EVARISTE GALOIS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.03945</t>
+          <t>701</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.35089</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>-13.07686</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.389529</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>353214</t>
+          <t>644671</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CORONEL FRANCISCO BOLOGNESI</t>
+          <t>MAZUBA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.06428</t>
+          <t>418</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.35575</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-13.07775</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.387429</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>352243</t>
+          <t>621561</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MARIA ENRIQUETA DOMINICI</t>
+          <t>GEUNI</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.07249</t>
+          <t>895</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.38225</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-13.07559</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.37633</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>730697</t>
+          <t>540174</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20975 ANDRES AVELINO CACERES DORREGARAY / 637</t>
+          <t>VILLA MARIA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.291588</t>
+          <t>616</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.247014</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>-13.065854</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.354992</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1131,22 +1131,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>-12.614426</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>-76.645582</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>352177</t>
+          <t>354204</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JOSE MARIA EGUREN</t>
+          <t>MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.0724</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.38649</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>-12.9432</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.384</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>540174</t>
+          <t>354138</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VILLA MARIA</t>
+          <t>20176</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.065854</t>
+          <t>518</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.354992</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>-12.975075</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.404409</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>351899</t>
+          <t>353884</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20191 ALFONSO UGARTE</t>
+          <t>20167 MANUEL GONZALES PRADA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.0772</t>
+          <t>854</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.38144</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>-13.017297</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.33846</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>351960</t>
+          <t>353266</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>21504 SAN JOSE / SAN JOSE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.07507</t>
+          <t>963</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.3872</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>-13.039766</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.351249</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>354138</t>
+          <t>353252</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20176</t>
+          <t>21505 NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.975075</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.404409</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>-13.03945</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.35089</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>351880</t>
+          <t>353214</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20190 REPUBLICA DE CHILE</t>
+          <t>CORONEL FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.08214</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.38711</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>-13.06428</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.35575</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>644671</t>
+          <t>353068</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MAZUBA</t>
+          <t>IMPERIAL C.N.I.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.07775</t>
+          <t>542</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.387429</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>-13.064703</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-76.352767</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>730230</t>
+          <t>353030</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>21531 MARIA AUXILIADORA</t>
+          <t>20147 ELADIO HURTADO VICENTE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-13.1357</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.3455</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>-13.061447</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-76.346668</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>352813</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MARYLAND BILINGUAL HIGH SCHOOL</t>
+          <t>VIRGEN DE LA CANDELARIA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-13.0837</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.388833</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>-12.51761</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-76.73491</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>354204</t>
+          <t>352728</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU</t>
+          <t>20960</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.9432</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.384</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>-12.542136</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-76.721557</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>352144</t>
+          <t>352653</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ROSA DE SANTA MARIA</t>
+          <t>REYNA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.07596</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.37905</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>-13.02597</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.47944</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>352163</t>
+          <t>352243</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MATER CHRISTI</t>
+          <t>MARIA ENRIQUETA DOMINICI</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-13.07555</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.38844</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>-13.07249</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.38225</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>353068</t>
+          <t>352177</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IMPERIAL C.N.I.</t>
+          <t>JOSE MARIA EGUREN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-13.064703</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.352767</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>-13.0724</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.38649</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>621561</t>
+          <t>352163</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GEUNI</t>
+          <t>MATER CHRISTI</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-13.07559</t>
+          <t>647</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.37633</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>-13.07555</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.38844</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>353884</t>
+          <t>352144</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20167 MANUEL GONZALES PRADA</t>
+          <t>ROSA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-13.017297</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.33846</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>-13.07596</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-76.37905</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>830932</t>
+          <t>352097</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PROLOG DE CAÑETE</t>
+          <t>VICTORIA BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-13.06591</t>
+          <t>772</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.35438</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>-13.07398</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-76.37556</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>352097</t>
+          <t>352021</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>VICTORIA BARCIA BONIFFATTI</t>
+          <t>SANTA RITA DE CASSIA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-13.07398</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.37556</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>-13.08496</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-76.38696</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>730193</t>
+          <t>352002</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>EVARISTE GALOIS</t>
+          <t>JOSE BUENAVENTURA SEPULVEDA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-13.07686</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.389529</t>
+          <t>91</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>-13.07666</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-76.38925</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>353266</t>
+          <t>351960</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>21504 SAN JOSE / SAN JOSE</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-13.039766</t>
+          <t>604</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.351249</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>-13.07507</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-76.3872</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>351804</t>
+          <t>351903</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-13.07634</t>
+          <t>345</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.38626</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>-13.07349</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-76.38082</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>351875</t>
+          <t>351899</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20189 NUESTRA SEÑORA DE LA CONCEPCION / 617</t>
+          <t>20191 ALFONSO UGARTE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-13.07468</t>
+          <t>509</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.38602</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>-13.0772</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-76.38144</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>353030</t>
+          <t>351880</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20147 ELADIO HURTADO VICENTE</t>
+          <t>20190 REPUBLICA DE CHILE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-13.061447</t>
+          <t>617</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.346668</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>-13.08214</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-76.38711</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>352021</t>
+          <t>351875</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SANTA RITA DE CASSIA</t>
+          <t>20189 NUESTRA SEÑORA DE LA CONCEPCION / 617</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-13.08496</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.38696</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>-13.07468</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-76.38602</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2619,22 +2619,22 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>1592</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>-13.0791</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>-76.3841</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1592</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>352728</t>
+          <t>351804</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.542136</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.721557</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-13.07634</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-76.38626</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>351757</t>
+          <t>351795</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>501 MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-13.07862</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.3838</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-13.07556</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.38423</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>352813</t>
+          <t>351757</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA CANDELARIA</t>
+          <t>481</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.51761</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.73491</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-13.07862</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.3838</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>352002</t>
+          <t>351682</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JOSE BUENAVENTURA SEPULVEDA</t>
+          <t>023</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-13.07666</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.38925</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>-13.08492</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-76.38731</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-CAÑETE-SAN_VICENTE_DE_CAÑETE.xlsx
+++ b/ZonasEscolares/excels/LIMA-CAÑETE-SAN_VICENTE_DE_CAÑETE.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
